--- a/example-en.xlsx
+++ b/example-en.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chatgpt\rack\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950CDD43-32C8-504F-ADCF-B6FE33D4B5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C777B6-D83D-4F64-9588-B1035BBDED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16860" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
   <sheets>
-    <sheet name="设备列表" sheetId="1" r:id="rId1"/>
-    <sheet name="模板说明" sheetId="2" r:id="rId2"/>
+    <sheet name="Device List" sheetId="1" r:id="rId1"/>
+    <sheet name="Template Notes" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,151 +37,174 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="42">
-  <si>
-    <t>设备名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>开始U位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>结束U位</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜4</t>
-  </si>
-  <si>
-    <t>机柜5</t>
-  </si>
-  <si>
-    <t>机柜7</t>
-  </si>
-  <si>
-    <t>机柜8</t>
-  </si>
-  <si>
-    <t>设备1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备2</t>
-  </si>
-  <si>
-    <t>设备3</t>
-  </si>
-  <si>
-    <t>设备4</t>
-  </si>
-  <si>
-    <t>设备7</t>
-  </si>
-  <si>
-    <t>设备8</t>
-  </si>
-  <si>
-    <t>设备9</t>
-  </si>
-  <si>
-    <t>设备11</t>
-  </si>
-  <si>
-    <t>设备12</t>
-  </si>
-  <si>
-    <t>设备13</t>
-  </si>
-  <si>
-    <t>设备14</t>
-  </si>
-  <si>
-    <t>机柜2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备类型</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>服务器</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>存储设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>网络设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>其他设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>小型机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>台式机</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备说明</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>说明文字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>序列号
-型号</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>安全设备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备5</t>
-  </si>
-  <si>
-    <t>设备6</t>
-  </si>
-  <si>
-    <t>设备10</t>
-  </si>
-  <si>
-    <t>机柜6</t>
-  </si>
-  <si>
-    <t>机柜3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>设备编号1234</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜1</t>
-  </si>
-  <si>
-    <t>http://rack.szqp.site</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>机柜图生成器</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="64">
+  <si>
+    <t>Device Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rack Name</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Start U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>End U</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rack 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rack 4</t>
+  </si>
+  <si>
+    <t>Rack 5</t>
+  </si>
+  <si>
+    <t>Rack 7</t>
+  </si>
+  <si>
+    <t>Rack 8</t>
+  </si>
+  <si>
+    <t>Device 1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device 2</t>
+  </si>
+  <si>
+    <t>Device 3</t>
+  </si>
+  <si>
+    <t>Device 4</t>
+  </si>
+  <si>
+    <t>Device 7</t>
+  </si>
+  <si>
+    <t>Device 8</t>
+  </si>
+  <si>
+    <t>Device 9</t>
+  </si>
+  <si>
+    <t>Device 11</t>
+  </si>
+  <si>
+    <t>Device 12</t>
+  </si>
+  <si>
+    <t>Device 13</t>
+  </si>
+  <si>
+    <t>Device 14</t>
+  </si>
+  <si>
+    <t>Rack 2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device Type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Server</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Storage Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Network Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Other Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Minicomputer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Desktop PC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Sample description</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Security Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Device 5</t>
+  </si>
+  <si>
+    <t>Device 6</t>
+  </si>
+  <si>
+    <t>Device 10</t>
+  </si>
+  <si>
+    <t>Rack 6</t>
+  </si>
+  <si>
+    <t>Rack 3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Rack 1</t>
+  </si>
+  <si>
+    <t>Rack Diagram Generator</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Model</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Serial No.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dell R760</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM FS5600</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>765321</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM 9117-MMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78H1234</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Core storage</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Transaction host</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -194,7 +217,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>模板使用说明：</t>
+      <t>Template Instructions:</t>
     </r>
     <r>
       <rPr>
@@ -216,7 +239,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>1. 请确保根据”</t>
+      <t>1. Complete the “</t>
     </r>
     <r>
       <rPr>
@@ -227,7 +250,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>设备列表</t>
+      <t>Device List</t>
     </r>
     <r>
       <rPr>
@@ -237,8 +260,8 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“Sheet的列进行填写，每行填写一个设备的信息。
-2.”</t>
+      <t>” worksheet using its column headings. Enter one device per row.
+2.</t>
     </r>
     <r>
       <rPr>
@@ -246,10 +269,10 @@
         <sz val="14"/>
         <color theme="7"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备说明</t>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“Model”</t>
     </r>
     <r>
       <rPr>
@@ -259,8 +282,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“列可留空，其他列都需填写完整。
-3. 设备的序列号、用途等可填写在”</t>
+      <t>, </t>
     </r>
     <r>
       <rPr>
@@ -268,10 +290,10 @@
         <sz val="14"/>
         <color theme="7"/>
         <rFont val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>设备说明</t>
+        <family val="4"/>
+        <charset val="134"/>
+      </rPr>
+      <t>“Serial No.”</t>
     </r>
     <r>
       <rPr>
@@ -281,20 +303,64 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“列，但考虑到美观，不宜填写过多内容。
-4. 设备的开始和结束U位不能重叠或冲突，不支持同一个U部署多个设备。若设备U位存在冲突，上传后会提示并跳过冲突设备。
-5.默认的设备类型包括”</t>
+      <t>, and “</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="14"/>
+        <color theme="7"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>” may be left blank; all other fields are required.
+3. Enter device purpose or notes in “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
+        <color theme="7"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>Description</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color theme="1"/>
+        <rFont val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>”. Keep the text brief for a clear layout.
+4. Start and end U positions must not overlap or conflict. Only one device can occupy a U position.
+   Conflicting devices will be flagged after upload.
+5. Default device types include “</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="14"/>
         <color theme="5"/>
         <rFont val="等线"/>
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>服务器</t>
+      <t>Server</t>
     </r>
     <r>
       <rPr>
@@ -304,7 +370,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>”, “</t>
     </r>
     <r>
       <rPr>
@@ -315,7 +381,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>存储设备</t>
+      <t>Storage Device</t>
     </r>
     <r>
       <rPr>
@@ -325,7 +391,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>”, “</t>
     </r>
     <r>
       <rPr>
@@ -336,7 +402,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>网络设备</t>
+      <t>Network Device</t>
     </r>
     <r>
       <rPr>
@@ -346,7 +412,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>”, “</t>
     </r>
     <r>
       <rPr>
@@ -357,7 +423,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>安全设</t>
+      <t>Security</t>
     </r>
     <r>
       <rPr>
@@ -367,7 +433,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>备</t>
+      <t> Device</t>
     </r>
     <r>
       <rPr>
@@ -377,7 +443,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“、”</t>
+      <t>”, “</t>
     </r>
     <r>
       <rPr>
@@ -388,7 +454,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>小型机</t>
+      <t>Minicomputer</t>
     </r>
     <r>
       <rPr>
@@ -398,7 +464,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“，不属于这四种的会被归类为”</t>
+      <t>”. Devices outside these types are classified as “</t>
     </r>
     <r>
       <rPr>
@@ -409,7 +475,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>其他</t>
+      <t>Other</t>
     </r>
     <r>
       <rPr>
@@ -419,9 +485,10 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>“，不同设备类型会对应不同的颜色，可以在机柜图生成器页面自定义颜色和增加更多分类。
-6.默认输出的布局图每排5个机柜，每个机柜42U，可在在机柜图生成器页面自定义。
-7.模板”</t>
+      <t>”. Each type has a different color.
+   Customize colors and add categories on the Rack Diagram Generator page.
+6. The default layout has 5 racks per row and 42U per rack. Customize these on the Rack Diagram Generator page.
+7. Red entries in the “</t>
     </r>
     <r>
       <rPr>
@@ -432,7 +499,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t>设备列表</t>
+      <t>Device List</t>
     </r>
     <r>
       <rPr>
@@ -442,9 +509,63 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t xml:space="preserve">“Sheet中红色内容为样例，可以删除，但需要保留第一列表头，且表头名称不能修改。
+      <t xml:space="preserve">” worksheet are examples and may be deleted. Keep the first row of headers and do not rename them.
 </t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>IBM SAN-B24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SAN switch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78H1235</t>
+  </si>
+  <si>
+    <t>78H1236</t>
+  </si>
+  <si>
+    <t>78H1237</t>
+  </si>
+  <si>
+    <t>78H1238</t>
+  </si>
+  <si>
+    <t>78H1239</t>
+  </si>
+  <si>
+    <t>78H1240</t>
+  </si>
+  <si>
+    <t>78H1241</t>
+  </si>
+  <si>
+    <t>78H1242</t>
+  </si>
+  <si>
+    <t>78H1243</t>
+  </si>
+  <si>
+    <t>78H1244</t>
+  </si>
+  <si>
+    <t>IPS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Voice Device</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AWAYA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://rack-web.szqp.site</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -452,7 +573,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -620,7 +741,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -630,8 +751,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -984,15 +1114,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D994C1D-E910-5148-8DBD-CEDB986AF5A3}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="8" max="8" width="41.83203125" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
+    <col min="7" max="7" width="10.875" style="6"/>
+    <col min="8" max="8" width="41.875" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
@@ -1008,13 +1140,17 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -1028,15 +1164,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="2">
-        <v>2</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="4">
+        <v>123456</v>
+      </c>
+      <c r="H2" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="34">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
@@ -1052,13 +1192,17 @@
       <c r="E3" s="2">
         <v>5</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="F3" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>23</v>
       </c>
@@ -1074,13 +1218,15 @@
       <c r="E4" s="2">
         <v>11</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="F4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>26</v>
       </c>
@@ -1088,7 +1234,7 @@
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2">
         <v>15</v>
@@ -1096,19 +1242,25 @@
       <c r="E5" s="2">
         <v>19</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="F5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>32</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D6" s="2">
         <v>20</v>
@@ -1116,19 +1268,23 @@
       <c r="E6" s="2">
         <v>22</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="F6" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D7" s="2">
         <v>30</v>
@@ -1136,11 +1292,13 @@
       <c r="E7" s="2">
         <v>35</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="F7" s="4"/>
+      <c r="G7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>24</v>
       </c>
@@ -1148,7 +1306,7 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2">
         <v>40</v>
@@ -1156,11 +1314,13 @@
       <c r="E8" s="2">
         <v>42</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="F8" s="4"/>
+      <c r="G8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1176,11 +1336,13 @@
       <c r="E9" s="2">
         <v>4</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="F9" s="4"/>
+      <c r="G9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>22</v>
       </c>
@@ -1188,7 +1350,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2">
         <v>7</v>
@@ -1196,16 +1358,18 @@
       <c r="E10" s="2">
         <v>15</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="F10" s="4"/>
+      <c r="G10" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>5</v>
@@ -1216,11 +1380,13 @@
       <c r="E11" s="2">
         <v>42</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="F11" s="4"/>
+      <c r="G11" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
@@ -1236,11 +1402,13 @@
       <c r="E12" s="2">
         <v>6</v>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="F12" s="4"/>
+      <c r="G12" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>25</v>
       </c>
@@ -1248,7 +1416,7 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2">
         <v>9</v>
@@ -1256,11 +1424,13 @@
       <c r="E13" s="2">
         <v>18</v>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="F13" s="4"/>
+      <c r="G13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>22</v>
       </c>
@@ -1276,13 +1446,15 @@
       <c r="E14" s="2">
         <v>12</v>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="F14" s="4"/>
+      <c r="G14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="H14" s="4"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>19</v>
@@ -1296,9 +1468,15 @@
       <c r="E15" s="2">
         <v>4</v>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="F15" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>61</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1310,168 +1488,168 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBC7C08-94AB-6E40-82CC-9BA77B7FD227}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="6" max="6" width="71.33203125" customWidth="1"/>
+    <col min="6" max="6" width="71.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="40" customHeight="1">
-      <c r="A1" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1">
-      <c r="A2" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="5"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="5"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="5"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
+    <row r="1" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="8"/>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8"/>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="8"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="8"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="8"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="8"/>
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="8"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="8"/>
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="8"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="8"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/example-en.xlsx
+++ b/example-en.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10609"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\chatgpt\rack\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qp/chatgpt/rack/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04C777B6-D83D-4F64-9588-B1035BBDED5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66D320EB-41A4-CA42-895D-4CB36BDD3228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="21840" windowHeight="13140" activeTab="1" xr2:uid="{AA460453-ECD7-0347-8816-907E34CDA78E}"/>
   </bookViews>
   <sheets>
     <sheet name="Device List" sheetId="1" r:id="rId1"/>
@@ -282,7 +282,7 @@
         <family val="3"/>
         <charset val="134"/>
       </rPr>
-      <t>, </t>
+      <t>,</t>
     </r>
     <r>
       <rPr>
@@ -433,7 +433,7 @@
         <family val="4"/>
         <charset val="134"/>
       </rPr>
-      <t> Device</t>
+      <t>Device</t>
     </r>
     <r>
       <rPr>
@@ -573,7 +573,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -695,7 +695,7 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -705,6 +705,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -745,9 +751,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -777,6 +780,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1114,367 +1120,367 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D994C1D-E910-5148-8DBD-CEDB986AF5A3}">
   <dimension ref="A1:H15"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="6" max="6" width="16.5" style="6" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="6"/>
-    <col min="8" max="8" width="41.875" style="6" customWidth="1"/>
+    <col min="6" max="6" width="16.5" style="5" customWidth="1"/>
+    <col min="7" max="7" width="10.83203125" style="5"/>
+    <col min="8" max="8" width="41.83203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:8">
+      <c r="A1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:8">
+      <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2" s="3">
         <v>123456</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:8" ht="17">
+      <c r="A3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3" s="1">
         <v>3</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3" s="1">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+    <row r="4" spans="1:8">
+      <c r="A4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>8</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>11</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="3"/>
+      <c r="H4" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>15</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>19</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6" s="1">
         <v>20</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="1">
         <v>22</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="H6" s="3"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7" s="1">
         <v>30</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7" s="1">
         <v>35</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
+      <c r="F7" s="3"/>
+      <c r="G7" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="H7" s="3"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8" s="1">
         <v>40</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8" s="1">
         <v>42</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
+      <c r="F8" s="3"/>
+      <c r="G8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="H8" s="3"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="1">
         <v>4</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
+      <c r="F9" s="3"/>
+      <c r="G9" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="H9" s="3"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>7</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="1">
         <v>15</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
+      <c r="F10" s="3"/>
+      <c r="G10" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="H10" s="3"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>41</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="1">
         <v>42</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
+      <c r="F11" s="3"/>
+      <c r="G11" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="H11" s="3"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>2</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="1">
         <v>6</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="3"/>
+      <c r="G12" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="H12" s="3"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>9</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="1">
         <v>18</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
+      <c r="F13" s="3"/>
+      <c r="G13" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>10</v>
       </c>
-      <c r="E14" s="2">
+      <c r="E14" s="1">
         <v>12</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="3"/>
+      <c r="G14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="H14" s="4"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="H14" s="3"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>1</v>
       </c>
-      <c r="E15" s="2">
+      <c r="E15" s="1">
         <v>4</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>61</v>
       </c>
     </row>
@@ -1488,168 +1494,168 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FBC7C08-94AB-6E40-82CC-9BA77B7FD227}">
   <dimension ref="A1:F19"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
-    <col min="6" max="6" width="71.375" customWidth="1"/>
+    <col min="6" max="6" width="71.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:6" ht="40" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-    </row>
-    <row r="2" spans="1:6" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="9" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+    </row>
+    <row r="2" spans="1:6" ht="36" customHeight="1">
+      <c r="A2" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="8"/>
-      <c r="B4" s="8"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="8"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
-      <c r="D5" s="8"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8"/>
-      <c r="C6" s="8"/>
-      <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="8"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="8"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="8"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
+      <c r="B3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="7"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="3">
